--- a/worksheets/iscp-data-collection.xlsx
+++ b/worksheets/iscp-data-collection.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A47"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -702,90 +702,97 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">   each process uses. Without that link there is no way to get from 'payroll matters most' to</t>
+          <t xml:space="preserve">   each process uses. They do not forbid it either, and working out a recovery order requires it,</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">   'therefore restore the database first', so no recovery order can be produced at all.</t>
+          <t xml:space="preserve">   so this is a prerequisite rather than an extra. Without that link there is no way to get from</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   'payroll matters most' to 'therefore restore the database first', and no recovery order exists.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>3. These are the business's numbers, not IT's.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Do not work out an objective from what the system can currently do. State what the business</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">   needs, then judge the architecture against it. That comparison is the entire value of the</t>
+          <t xml:space="preserve">   Do not work out an objective from what the system can currently do. State what the business</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t xml:space="preserve">   needs, then judge the architecture against it. That comparison is the entire value of the</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t xml:space="preserve">   exercise, and it disappears if the requirement is copied from the capability.</t>
         </is>
       </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>HOW TO FILL A CELL YOU DO NOT KNOW</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr"/>
-    </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Leave it blank. A blank cell is reported as missing and somebody gets asked.</t>
-        </is>
-      </c>
+      <c r="A43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>Leave it blank. A blank cell is reported as missing and somebody gets asked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>A guess is reported as an answer and nobody ever checks it again.</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr"/>
-    </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Orange columns are required. Yellow columns are worked out from other tabs; fill them only to</t>
-        </is>
-      </c>
+      <c r="A46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
+        <is>
+          <t>Orange columns are required. Yellow columns are worked out from other tabs; fill them only to</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>override, and say why in the notes column when you do.</t>
         </is>
@@ -9728,7 +9735,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>THE TAB EVERYBODY SKIPS. One row for every pairing: which components does each process actually need in order to work? Both columns are dropdowns, so you cannot invent either side. Without this tab there is no way to turn 'payroll matters most' into 'therefore restore the database first', and no recovery order can be produced at all. Standard templates do not ask for this. That is why so many plans cannot answer what to fix first.</t>
+          <t>THE TAB EVERYBODY SKIPS. One row for every pairing: which components does each process actually need in order to work? Both columns are dropdowns, so you cannot invent either side. Without this tab there is no way to turn 'payroll matters most' into 'therefore restore the database first', and no recovery order can be produced at all. No standard template prompts for this and none forbids it: working out a recovery order requires it, so it is a prerequisite rather than an extra. That is why so many plans cannot answer what to fix first.</t>
         </is>
       </c>
     </row>
